--- a/templates/spreading/default_spreading_template.xlsx
+++ b/templates/spreading/default_spreading_template.xlsx
@@ -423,13 +423,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -453,6 +459,36 @@
           <t>FY-Current</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>FY+1</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>FY+2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>FY+3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>FY+1 (Downside)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>FY+2 (Downside)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>FY+3 (Downside)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -493,6 +529,30 @@
         <f>D3-D4</f>
         <v/>
       </c>
+      <c r="E5">
+        <f>E3-E4</f>
+        <v/>
+      </c>
+      <c r="F5">
+        <f>F3-F4</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>G3-G4</f>
+        <v/>
+      </c>
+      <c r="H5">
+        <f>H3-H4</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>I3-I4</f>
+        <v/>
+      </c>
+      <c r="J5">
+        <f>J3-J4</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -501,15 +561,39 @@
         </is>
       </c>
       <c r="B6">
-        <f>IFERROR(B5/B3,0)</f>
+        <f>IFERROR(B5/B3,"N/A")</f>
         <v/>
       </c>
       <c r="C6">
-        <f>IFERROR(C5/C3,0)</f>
+        <f>IFERROR(C5/C3,"N/A")</f>
         <v/>
       </c>
       <c r="D6">
-        <f>IFERROR(D5/D3,0)</f>
+        <f>IFERROR(D5/D3,"N/A")</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>IFERROR(E5/E3,"N/A")</f>
+        <v/>
+      </c>
+      <c r="F6">
+        <f>IFERROR(F5/F3,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>IFERROR(G5/G3,"N/A")</f>
+        <v/>
+      </c>
+      <c r="H6">
+        <f>IFERROR(H5/H3,"N/A")</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>IFERROR(I5/I3,"N/A")</f>
+        <v/>
+      </c>
+      <c r="J6">
+        <f>IFERROR(J5/J3,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -559,6 +643,30 @@
         <f>D5-D7-D8-D9+D10</f>
         <v/>
       </c>
+      <c r="E11">
+        <f>E5-E7-E8-E9+E10</f>
+        <v/>
+      </c>
+      <c r="F11">
+        <f>F5-F7-F8-F9+F10</f>
+        <v/>
+      </c>
+      <c r="G11">
+        <f>G5-G7-G8-G9+G10</f>
+        <v/>
+      </c>
+      <c r="H11">
+        <f>H5-H7-H8-H9+H10</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>I5-I7-I8-I9+I10</f>
+        <v/>
+      </c>
+      <c r="J11">
+        <f>J5-J7-J8-J9+J10</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -567,15 +675,39 @@
         </is>
       </c>
       <c r="B12">
-        <f>IFERROR(B11/B3,0)</f>
+        <f>IFERROR(B11/B3,"N/A")</f>
         <v/>
       </c>
       <c r="C12">
-        <f>IFERROR(C11/C3,0)</f>
+        <f>IFERROR(C11/C3,"N/A")</f>
         <v/>
       </c>
       <c r="D12">
-        <f>IFERROR(D11/D3,0)</f>
+        <f>IFERROR(D11/D3,"N/A")</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>IFERROR(E11/E3,"N/A")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>IFERROR(F11/F3,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>IFERROR(G11/G3,"N/A")</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>IFERROR(H11/H3,"N/A")</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>IFERROR(I11/I3,"N/A")</f>
+        <v/>
+      </c>
+      <c r="J12">
+        <f>IFERROR(J11/J3,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -597,6 +729,30 @@
         <f>D11+D8+D9</f>
         <v/>
       </c>
+      <c r="E13">
+        <f>E11+E8+E9</f>
+        <v/>
+      </c>
+      <c r="F13">
+        <f>F11+F8+F9</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>G11+G8+G9</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>H11+H8+H9</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>I11+I8+I9</f>
+        <v/>
+      </c>
+      <c r="J13">
+        <f>J11+J8+J9</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -622,524 +778,1092 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Exceptional Costs / (Income)</t>
+          <t>Capital Expenditure</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Profit Before Tax</t>
-        </is>
-      </c>
-      <c r="B18">
-        <f>B11-B14+B15-B17</f>
-        <v/>
-      </c>
-      <c r="C18">
-        <f>C11-C14+C15-C17</f>
-        <v/>
-      </c>
-      <c r="D18">
-        <f>D11-D14+D15-D17</f>
-        <v/>
+          <t>Exceptional Costs / (Income)</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tax</t>
-        </is>
+          <t>Profit Before Tax</t>
+        </is>
+      </c>
+      <c r="B19">
+        <f>B11-B14+B15-B18</f>
+        <v/>
+      </c>
+      <c r="C19">
+        <f>C11-C14+C15-C18</f>
+        <v/>
+      </c>
+      <c r="D19">
+        <f>D11-D14+D15-D18</f>
+        <v/>
+      </c>
+      <c r="E19">
+        <f>E11-E14+E15-E18</f>
+        <v/>
+      </c>
+      <c r="F19">
+        <f>F11-F14+F15-F18</f>
+        <v/>
+      </c>
+      <c r="G19">
+        <f>G11-G14+G15-G18</f>
+        <v/>
+      </c>
+      <c r="H19">
+        <f>H11-H14+H15-H18</f>
+        <v/>
+      </c>
+      <c r="I19">
+        <f>I11-I14+I15-I18</f>
+        <v/>
+      </c>
+      <c r="J19">
+        <f>J11-J14+J15-J18</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Net Profit</t>
         </is>
       </c>
-      <c r="B20">
-        <f>B18-B19</f>
-        <v/>
-      </c>
-      <c r="C20">
-        <f>C18-C19</f>
-        <v/>
-      </c>
-      <c r="D20">
-        <f>D18-D19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="B21">
+        <f>B19-B20</f>
+        <v/>
+      </c>
+      <c r="C21">
+        <f>C19-C20</f>
+        <v/>
+      </c>
+      <c r="D21">
+        <f>D19-D20</f>
+        <v/>
+      </c>
+      <c r="E21">
+        <f>E19-E20</f>
+        <v/>
+      </c>
+      <c r="F21">
+        <f>F19-F20</f>
+        <v/>
+      </c>
+      <c r="G21">
+        <f>G19-G20</f>
+        <v/>
+      </c>
+      <c r="H21">
+        <f>H19-H20</f>
+        <v/>
+      </c>
+      <c r="I21">
+        <f>I19-I20</f>
+        <v/>
+      </c>
+      <c r="J21">
+        <f>J19-J20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Key Ratios</t>
         </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>DSCR</t>
-        </is>
-      </c>
-      <c r="B22">
-        <f>IFERROR(B13/(B14+B16),0)</f>
-        <v/>
-      </c>
-      <c r="C22">
-        <f>IFERROR(C13/(C14+C16),0)</f>
-        <v/>
-      </c>
-      <c r="D22">
-        <f>IFERROR(D13/(D14+D16),0)</f>
-        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EBIT/Interest</t>
+          <t>DSCR</t>
         </is>
       </c>
       <c r="B23">
-        <f>IFERROR(B11/B14,0)</f>
+        <f>IFERROR(B13/(B14+B16),"N/A")</f>
         <v/>
       </c>
       <c r="C23">
-        <f>IFERROR(C11/C14,0)</f>
+        <f>IFERROR(C13/(C14+C16),"N/A")</f>
         <v/>
       </c>
       <c r="D23">
-        <f>IFERROR(D11/D14,0)</f>
+        <f>IFERROR(D13/(D14+D16),"N/A")</f>
+        <v/>
+      </c>
+      <c r="E23">
+        <f>IFERROR(E13/(E14+E16),"N/A")</f>
+        <v/>
+      </c>
+      <c r="F23">
+        <f>IFERROR(F13/(F14+F16),"N/A")</f>
+        <v/>
+      </c>
+      <c r="G23">
+        <f>IFERROR(G13/(G14+G16),"N/A")</f>
+        <v/>
+      </c>
+      <c r="H23">
+        <f>IFERROR(H13/(H14+H16),"N/A")</f>
+        <v/>
+      </c>
+      <c r="I23">
+        <f>IFERROR(I13/(I14+I16),"N/A")</f>
+        <v/>
+      </c>
+      <c r="J23">
+        <f>IFERROR(J13/(J14+J16),"N/A")</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>EBIT/Interest</t>
+        </is>
+      </c>
+      <c r="B24">
+        <f>IFERROR(B11/B14,"N/A")</f>
+        <v/>
+      </c>
+      <c r="C24">
+        <f>IFERROR(C11/C14,"N/A")</f>
+        <v/>
+      </c>
+      <c r="D24">
+        <f>IFERROR(D11/D14,"N/A")</f>
+        <v/>
+      </c>
+      <c r="E24">
+        <f>IFERROR(E11/E14,"N/A")</f>
+        <v/>
+      </c>
+      <c r="F24">
+        <f>IFERROR(F11/F14,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G24">
+        <f>IFERROR(G11/G14,"N/A")</f>
+        <v/>
+      </c>
+      <c r="H24">
+        <f>IFERROR(H11/H14,"N/A")</f>
+        <v/>
+      </c>
+      <c r="I24">
+        <f>IFERROR(I11/I14,"N/A")</f>
+        <v/>
+      </c>
+      <c r="J24">
+        <f>IFERROR(J11/J14,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>EBITDA/Interest</t>
         </is>
       </c>
-      <c r="B24">
-        <f>IFERROR(B13/B14,0)</f>
-        <v/>
-      </c>
-      <c r="C24">
-        <f>IFERROR(C13/C14,0)</f>
-        <v/>
-      </c>
-      <c r="D24">
-        <f>IFERROR(D13/D14,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Balance Sheet</t>
-        </is>
+      <c r="B25">
+        <f>IFERROR(B13/B14,"N/A")</f>
+        <v/>
+      </c>
+      <c r="C25">
+        <f>IFERROR(C13/C14,"N/A")</f>
+        <v/>
+      </c>
+      <c r="D25">
+        <f>IFERROR(D13/D14,"N/A")</f>
+        <v/>
+      </c>
+      <c r="E25">
+        <f>IFERROR(E13/E14,"N/A")</f>
+        <v/>
+      </c>
+      <c r="F25">
+        <f>IFERROR(F13/F14,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G25">
+        <f>IFERROR(G13/G14,"N/A")</f>
+        <v/>
+      </c>
+      <c r="H25">
+        <f>IFERROR(H13/H14,"N/A")</f>
+        <v/>
+      </c>
+      <c r="I25">
+        <f>IFERROR(I13/I14,"N/A")</f>
+        <v/>
+      </c>
+      <c r="J25">
+        <f>IFERROR(J13/J14,"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Tangible Fixed Assets</t>
-        </is>
+          <t>FCF</t>
+        </is>
+      </c>
+      <c r="B26">
+        <f>B13-B17-B20-B14+B15</f>
+        <v/>
+      </c>
+      <c r="C26">
+        <f>C13-C17-C20-C14+C15</f>
+        <v/>
+      </c>
+      <c r="D26">
+        <f>D13-D17-D20-D14+D15</f>
+        <v/>
+      </c>
+      <c r="E26">
+        <f>E13-E17-E20-E14+E15</f>
+        <v/>
+      </c>
+      <c r="F26">
+        <f>F13-F17-F20-F14+F15</f>
+        <v/>
+      </c>
+      <c r="G26">
+        <f>G13-G17-G20-G14+G15</f>
+        <v/>
+      </c>
+      <c r="H26">
+        <f>H13-H17-H20-H14+H15</f>
+        <v/>
+      </c>
+      <c r="I26">
+        <f>I13-I17-I20-I14+I15</f>
+        <v/>
+      </c>
+      <c r="J26">
+        <f>J13-J17-J20-J14+J15</f>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Intangible Fixed Assets</t>
-        </is>
+          <t>FCF Conversion %</t>
+        </is>
+      </c>
+      <c r="B27">
+        <f>IFERROR(B26/B13,"N/A")</f>
+        <v/>
+      </c>
+      <c r="C27">
+        <f>IFERROR(C26/C13,"N/A")</f>
+        <v/>
+      </c>
+      <c r="D27">
+        <f>IFERROR(D26/D13,"N/A")</f>
+        <v/>
+      </c>
+      <c r="E27">
+        <f>IFERROR(E26/E13,"N/A")</f>
+        <v/>
+      </c>
+      <c r="F27">
+        <f>IFERROR(F26/F13,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G27">
+        <f>IFERROR(G26/G13,"N/A")</f>
+        <v/>
+      </c>
+      <c r="H27">
+        <f>IFERROR(H26/H13,"N/A")</f>
+        <v/>
+      </c>
+      <c r="I27">
+        <f>IFERROR(I26/I13,"N/A")</f>
+        <v/>
+      </c>
+      <c r="J27">
+        <f>IFERROR(J26/J13,"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Investments</t>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Balance Sheet</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Total Fixed Assets</t>
-        </is>
-      </c>
-      <c r="B29">
-        <f>B26+B27+B28</f>
-        <v/>
-      </c>
-      <c r="C29">
-        <f>C26+C27+C28</f>
-        <v/>
-      </c>
-      <c r="D29">
-        <f>D26+D27+D28</f>
-        <v/>
+          <t>Tangible Fixed Assets</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Intangible Fixed Assets</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
+          <t>Investments</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Stock</t>
-        </is>
+          <t>Total Fixed Assets</t>
+        </is>
+      </c>
+      <c r="B32">
+        <f>B29+B30+B31</f>
+        <v/>
+      </c>
+      <c r="C32">
+        <f>C29+C30+C31</f>
+        <v/>
+      </c>
+      <c r="D32">
+        <f>D29+D30+D31</f>
+        <v/>
+      </c>
+      <c r="E32">
+        <f>E29+E30+E31</f>
+        <v/>
+      </c>
+      <c r="F32">
+        <f>F29+F30+F31</f>
+        <v/>
+      </c>
+      <c r="G32">
+        <f>G29+G30+G31</f>
+        <v/>
+      </c>
+      <c r="H32">
+        <f>H29+H30+H31</f>
+        <v/>
+      </c>
+      <c r="I32">
+        <f>I29+I30+I31</f>
+        <v/>
+      </c>
+      <c r="J32">
+        <f>J29+J30+J31</f>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Other Current Assets</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Total Current Assets</t>
-        </is>
-      </c>
-      <c r="B34">
-        <f>B30+B31+B32+B33</f>
-        <v/>
-      </c>
-      <c r="C34">
-        <f>C30+C31+C32+C33</f>
-        <v/>
-      </c>
-      <c r="D34">
-        <f>D30+D31+D32+D33</f>
-        <v/>
+          <t>Accounts Receivable</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total Assets</t>
-        </is>
-      </c>
-      <c r="B35">
-        <f>B29+B34</f>
-        <v/>
-      </c>
-      <c r="C35">
-        <f>C29+C34</f>
-        <v/>
-      </c>
-      <c r="D35">
-        <f>D29+D34</f>
-        <v/>
+          <t>Stock</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Other Current Assets</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Current Portion - Debt</t>
-        </is>
+          <t>Total Current Assets</t>
+        </is>
+      </c>
+      <c r="B37">
+        <f>B33+B34+B35+B36</f>
+        <v/>
+      </c>
+      <c r="C37">
+        <f>C33+C34+C35+C36</f>
+        <v/>
+      </c>
+      <c r="D37">
+        <f>D33+D34+D35+D36</f>
+        <v/>
+      </c>
+      <c r="E37">
+        <f>E33+E34+E35+E36</f>
+        <v/>
+      </c>
+      <c r="F37">
+        <f>F33+F34+F35+F36</f>
+        <v/>
+      </c>
+      <c r="G37">
+        <f>G33+G34+G35+G36</f>
+        <v/>
+      </c>
+      <c r="H37">
+        <f>H33+H34+H35+H36</f>
+        <v/>
+      </c>
+      <c r="I37">
+        <f>I33+I34+I35+I36</f>
+        <v/>
+      </c>
+      <c r="J37">
+        <f>J33+J34+J35+J36</f>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Overdraft / Revolving Debt</t>
-        </is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B38">
+        <f>B32+B37</f>
+        <v/>
+      </c>
+      <c r="C38">
+        <f>C32+C37</f>
+        <v/>
+      </c>
+      <c r="D38">
+        <f>D32+D37</f>
+        <v/>
+      </c>
+      <c r="E38">
+        <f>E32+E37</f>
+        <v/>
+      </c>
+      <c r="F38">
+        <f>F32+F37</f>
+        <v/>
+      </c>
+      <c r="G38">
+        <f>G32+G37</f>
+        <v/>
+      </c>
+      <c r="H38">
+        <f>H32+H37</f>
+        <v/>
+      </c>
+      <c r="I38">
+        <f>I32+I37</f>
+        <v/>
+      </c>
+      <c r="J38">
+        <f>J32+J37</f>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Other Current Liabilities</t>
+          <t>Accounts Payable</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Total Current Liabilities</t>
-        </is>
-      </c>
-      <c r="B40">
-        <f>B36+B37+B38+B39</f>
-        <v/>
-      </c>
-      <c r="C40">
-        <f>C36+C37+C38+C39</f>
-        <v/>
-      </c>
-      <c r="D40">
-        <f>D36+D37+D38+D39</f>
-        <v/>
+          <t>Current Portion - Debt</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Long Term Debt</t>
+          <t>Overdraft / Revolving Debt</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Loan Notes / Preference Shares</t>
+          <t>Other Current Liabilities</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Other Long Term Liabilities</t>
-        </is>
+          <t>Total Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B43">
+        <f>B39+B40+B41+B42</f>
+        <v/>
+      </c>
+      <c r="C43">
+        <f>C39+C40+C41+C42</f>
+        <v/>
+      </c>
+      <c r="D43">
+        <f>D39+D40+D41+D42</f>
+        <v/>
+      </c>
+      <c r="E43">
+        <f>E39+E40+E41+E42</f>
+        <v/>
+      </c>
+      <c r="F43">
+        <f>F39+F40+F41+F42</f>
+        <v/>
+      </c>
+      <c r="G43">
+        <f>G39+G40+G41+G42</f>
+        <v/>
+      </c>
+      <c r="H43">
+        <f>H39+H40+H41+H42</f>
+        <v/>
+      </c>
+      <c r="I43">
+        <f>I39+I40+I41+I42</f>
+        <v/>
+      </c>
+      <c r="J43">
+        <f>J39+J40+J41+J42</f>
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Provisions</t>
+          <t>Long Term Debt</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Total Long Term Liabilities</t>
-        </is>
-      </c>
-      <c r="B45">
-        <f>B41+B42+B43+B44</f>
-        <v/>
-      </c>
-      <c r="C45">
-        <f>C41+C42+C43+C44</f>
-        <v/>
-      </c>
-      <c r="D45">
-        <f>D41+D42+D43+D44</f>
-        <v/>
+          <t>Loan Notes / Preference Shares</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Total Liabilities</t>
-        </is>
-      </c>
-      <c r="B46">
-        <f>B40+B45</f>
-        <v/>
-      </c>
-      <c r="C46">
-        <f>C40+C45</f>
-        <v/>
-      </c>
-      <c r="D46">
-        <f>D40+D45</f>
-        <v/>
+          <t>Other Long Term Liabilities</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Share Capital</t>
+          <t>Provisions</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Retained Profit</t>
-        </is>
+          <t>Total Long Term Liabilities</t>
+        </is>
+      </c>
+      <c r="B48">
+        <f>B44+B45+B46+B47</f>
+        <v/>
+      </c>
+      <c r="C48">
+        <f>C44+C45+C46+C47</f>
+        <v/>
+      </c>
+      <c r="D48">
+        <f>D44+D45+D46+D47</f>
+        <v/>
+      </c>
+      <c r="E48">
+        <f>E44+E45+E46+E47</f>
+        <v/>
+      </c>
+      <c r="F48">
+        <f>F44+F45+F46+F47</f>
+        <v/>
+      </c>
+      <c r="G48">
+        <f>G44+G45+G46+G47</f>
+        <v/>
+      </c>
+      <c r="H48">
+        <f>H44+H45+H46+H47</f>
+        <v/>
+      </c>
+      <c r="I48">
+        <f>I44+I45+I46+I47</f>
+        <v/>
+      </c>
+      <c r="J48">
+        <f>J44+J45+J46+J47</f>
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Total Equity</t>
+          <t>Total Liabilities</t>
         </is>
       </c>
       <c r="B49">
-        <f>B47+B48</f>
+        <f>B43+B48</f>
         <v/>
       </c>
       <c r="C49">
-        <f>C47+C48</f>
+        <f>C43+C48</f>
         <v/>
       </c>
       <c r="D49">
-        <f>D47+D48</f>
+        <f>D43+D48</f>
+        <v/>
+      </c>
+      <c r="E49">
+        <f>E43+E48</f>
+        <v/>
+      </c>
+      <c r="F49">
+        <f>F43+F48</f>
+        <v/>
+      </c>
+      <c r="G49">
+        <f>G43+G48</f>
+        <v/>
+      </c>
+      <c r="H49">
+        <f>H43+H48</f>
+        <v/>
+      </c>
+      <c r="I49">
+        <f>I43+I48</f>
+        <v/>
+      </c>
+      <c r="J49">
+        <f>J43+J48</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Key Credit Metrics</t>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share Capital</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Tangible Net Worth (TNW)</t>
-        </is>
-      </c>
-      <c r="B51">
-        <f>B49-B27</f>
-        <v/>
-      </c>
-      <c r="C51">
-        <f>C49-C27</f>
-        <v/>
-      </c>
-      <c r="D51">
-        <f>D49-D27</f>
-        <v/>
+          <t>Retained Profit</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TNW + Loan Notes / Preference Shares</t>
+          <t>Total Equity</t>
         </is>
       </c>
       <c r="B52">
-        <f>B51+B42</f>
+        <f>B50+B51</f>
         <v/>
       </c>
       <c r="C52">
-        <f>C51+C42</f>
+        <f>C50+C51</f>
         <v/>
       </c>
       <c r="D52">
-        <f>D51+D42</f>
+        <f>D50+D51</f>
+        <v/>
+      </c>
+      <c r="E52">
+        <f>E50+E51</f>
+        <v/>
+      </c>
+      <c r="F52">
+        <f>F50+F51</f>
+        <v/>
+      </c>
+      <c r="G52">
+        <f>G50+G51</f>
+        <v/>
+      </c>
+      <c r="H52">
+        <f>H50+H51</f>
+        <v/>
+      </c>
+      <c r="I52">
+        <f>I50+I51</f>
+        <v/>
+      </c>
+      <c r="J52">
+        <f>J50+J51</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Gearing % (Interest-Bearing Debt / Equity)</t>
-        </is>
-      </c>
-      <c r="B53">
-        <f>IFERROR((B37+B38+B41+B42)/B49,0)</f>
-        <v/>
-      </c>
-      <c r="C53">
-        <f>IFERROR((C37+C38+C41+C42)/C49,0)</f>
-        <v/>
-      </c>
-      <c r="D53">
-        <f>IFERROR((D37+D38+D41+D42)/D49,0)</f>
-        <v/>
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Key Credit Metrics</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Current Ratio</t>
+          <t>Tangible Net Worth (TNW)</t>
         </is>
       </c>
       <c r="B54">
-        <f>IFERROR(B34/B40,0)</f>
+        <f>B52-B30</f>
         <v/>
       </c>
       <c r="C54">
-        <f>IFERROR(C34/C40,0)</f>
+        <f>C52-C30</f>
         <v/>
       </c>
       <c r="D54">
-        <f>IFERROR(D34/D40,0)</f>
+        <f>D52-D30</f>
+        <v/>
+      </c>
+      <c r="E54">
+        <f>E52-E30</f>
+        <v/>
+      </c>
+      <c r="F54">
+        <f>F52-F30</f>
+        <v/>
+      </c>
+      <c r="G54">
+        <f>G52-G30</f>
+        <v/>
+      </c>
+      <c r="H54">
+        <f>H52-H30</f>
+        <v/>
+      </c>
+      <c r="I54">
+        <f>I52-I30</f>
+        <v/>
+      </c>
+      <c r="J54">
+        <f>J52-J30</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Gross Leverage</t>
+          <t>TNW + Loan Notes / Preference Shares</t>
         </is>
       </c>
       <c r="B55">
-        <f>IFERROR((B37+B38+B41+B42)/B13,0)</f>
+        <f>B54+B45</f>
         <v/>
       </c>
       <c r="C55">
-        <f>IFERROR((C37+C38+C41+C42)/C13,0)</f>
+        <f>C54+C45</f>
         <v/>
       </c>
       <c r="D55">
-        <f>IFERROR((D37+D38+D41+D42)/D13,0)</f>
+        <f>D54+D45</f>
+        <v/>
+      </c>
+      <c r="E55">
+        <f>E54+E45</f>
+        <v/>
+      </c>
+      <c r="F55">
+        <f>F54+F45</f>
+        <v/>
+      </c>
+      <c r="G55">
+        <f>G54+G45</f>
+        <v/>
+      </c>
+      <c r="H55">
+        <f>H54+H45</f>
+        <v/>
+      </c>
+      <c r="I55">
+        <f>I54+I45</f>
+        <v/>
+      </c>
+      <c r="J55">
+        <f>J54+J45</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Working Capital</t>
-        </is>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Gearing % (Interest-Bearing Debt / Equity)</t>
+        </is>
+      </c>
+      <c r="B56">
+        <f>IFERROR((B40+B41+B44+B45)/B52,"N/A")</f>
+        <v/>
+      </c>
+      <c r="C56">
+        <f>IFERROR((C40+C41+C44+C45)/C52,"N/A")</f>
+        <v/>
+      </c>
+      <c r="D56">
+        <f>IFERROR((D40+D41+D44+D45)/D52,"N/A")</f>
+        <v/>
+      </c>
+      <c r="E56">
+        <f>IFERROR((E40+E41+E44+E45)/E52,"N/A")</f>
+        <v/>
+      </c>
+      <c r="F56">
+        <f>IFERROR((F40+F41+F44+F45)/F52,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G56">
+        <f>IFERROR((G40+G41+G44+G45)/G52,"N/A")</f>
+        <v/>
+      </c>
+      <c r="H56">
+        <f>IFERROR((H40+H41+H44+H45)/H52,"N/A")</f>
+        <v/>
+      </c>
+      <c r="I56">
+        <f>IFERROR((I40+I41+I44+I45)/I52,"N/A")</f>
+        <v/>
+      </c>
+      <c r="J56">
+        <f>IFERROR((J40+J41+J44+J45)/J52,"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Trade Debtor Days</t>
-        </is>
+          <t>Current Ratio</t>
+        </is>
+      </c>
+      <c r="B57">
+        <f>IFERROR(B37/B43,"N/A")</f>
+        <v/>
+      </c>
+      <c r="C57">
+        <f>IFERROR(C37/C43,"N/A")</f>
+        <v/>
+      </c>
+      <c r="D57">
+        <f>IFERROR(D37/D43,"N/A")</f>
+        <v/>
+      </c>
+      <c r="E57">
+        <f>IFERROR(E37/E43,"N/A")</f>
+        <v/>
+      </c>
+      <c r="F57">
+        <f>IFERROR(F37/F43,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G57">
+        <f>IFERROR(G37/G43,"N/A")</f>
+        <v/>
+      </c>
+      <c r="H57">
+        <f>IFERROR(H37/H43,"N/A")</f>
+        <v/>
+      </c>
+      <c r="I57">
+        <f>IFERROR(I37/I43,"N/A")</f>
+        <v/>
+      </c>
+      <c r="J57">
+        <f>IFERROR(J37/J43,"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Trade Creditor Days</t>
-        </is>
+          <t>Gross Leverage</t>
+        </is>
+      </c>
+      <c r="B58">
+        <f>IFERROR((B40+B41+B44+B45)/B13,"N/A")</f>
+        <v/>
+      </c>
+      <c r="C58">
+        <f>IFERROR((C40+C41+C44+C45)/C13,"N/A")</f>
+        <v/>
+      </c>
+      <c r="D58">
+        <f>IFERROR((D40+D41+D44+D45)/D13,"N/A")</f>
+        <v/>
+      </c>
+      <c r="E58">
+        <f>IFERROR((E40+E41+E44+E45)/E13,"N/A")</f>
+        <v/>
+      </c>
+      <c r="F58">
+        <f>IFERROR((F40+F41+F44+F45)/F13,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G58">
+        <f>IFERROR((G40+G41+G44+G45)/G13,"N/A")</f>
+        <v/>
+      </c>
+      <c r="H58">
+        <f>IFERROR((H40+H41+H44+H45)/H13,"N/A")</f>
+        <v/>
+      </c>
+      <c r="I58">
+        <f>IFERROR((I40+I41+I44+I45)/I13,"N/A")</f>
+        <v/>
+      </c>
+      <c r="J58">
+        <f>IFERROR((J40+J41+J44+J45)/J13,"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>Net Debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B59">
+        <f>IFERROR((B40+B41+B44+B45-B33)/B13,"N/A")</f>
+        <v/>
+      </c>
+      <c r="C59">
+        <f>IFERROR((C40+C41+C44+C45-C33)/C13,"N/A")</f>
+        <v/>
+      </c>
+      <c r="D59">
+        <f>IFERROR((D40+D41+D44+D45-D33)/D13,"N/A")</f>
+        <v/>
+      </c>
+      <c r="E59">
+        <f>IFERROR((E40+E41+E44+E45-E33)/E13,"N/A")</f>
+        <v/>
+      </c>
+      <c r="F59">
+        <f>IFERROR((F40+F41+F44+F45-F33)/F13,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G59">
+        <f>IFERROR((G40+G41+G44+G45-G33)/G13,"N/A")</f>
+        <v/>
+      </c>
+      <c r="H59">
+        <f>IFERROR((H40+H41+H44+H45-H33)/H13,"N/A")</f>
+        <v/>
+      </c>
+      <c r="I59">
+        <f>IFERROR((I40+I41+I44+I45-I33)/I13,"N/A")</f>
+        <v/>
+      </c>
+      <c r="J59">
+        <f>IFERROR((J40+J41+J44+J45-J33)/J13,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Trade Debtor Days</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Trade Creditor Days</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>Stock Days</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>Working Capital Cycle (days)</t>
         </is>
       </c>
-      <c r="B60">
-        <f>B57+B59-B58</f>
-        <v/>
-      </c>
-      <c r="C60">
-        <f>C57+C59-C58</f>
-        <v/>
-      </c>
-      <c r="D60">
-        <f>D57+D59-D58</f>
+      <c r="B64">
+        <f>B61+B63-B62</f>
+        <v/>
+      </c>
+      <c r="C64">
+        <f>C61+C63-C62</f>
+        <v/>
+      </c>
+      <c r="D64">
+        <f>D61+D63-D62</f>
+        <v/>
+      </c>
+      <c r="E64">
+        <f>E61+E63-E62</f>
+        <v/>
+      </c>
+      <c r="F64">
+        <f>F61+F63-F62</f>
+        <v/>
+      </c>
+      <c r="G64">
+        <f>G61+G63-G62</f>
+        <v/>
+      </c>
+      <c r="H64">
+        <f>H61+H63-H62</f>
+        <v/>
+      </c>
+      <c r="I64">
+        <f>I61+I63-I62</f>
+        <v/>
+      </c>
+      <c r="J64">
+        <f>J61+J63-J62</f>
         <v/>
       </c>
     </row>
@@ -1217,7 +1941,7 @@
     </row>
     <row r="2">
       <c r="H2">
-        <f>IFERROR(G2/B2,0)</f>
+        <f>IFERROR(G2/B2,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1252,7 +1976,7 @@
         <v/>
       </c>
       <c r="H3">
-        <f>IFERROR(G3/B3,0)</f>
+        <f>IFERROR(G3/B3,"N/A")</f>
         <v/>
       </c>
     </row>

--- a/templates/spreading/default_spreading_template.xlsx
+++ b/templates/spreading/default_spreading_template.xlsx
@@ -132,6 +132,257 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Leverage Trend</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Financial Spreading'!$A$58</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Financial Spreading'!$B$1:$G$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Financial Spreading'!$B$58:$G$58</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Financial Spreading'!$A$59</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Financial Spreading'!$B$1:$G$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Financial Spreading'!$B$59:$G$59</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Revenue Trend</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Financial Spreading'!$A$3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Financial Spreading'!$B$1:$G$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Financial Spreading'!$B$3:$G$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>65</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>83</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -561,39 +812,39 @@
         </is>
       </c>
       <c r="B6">
-        <f>IFERROR(B5/B3,"N/A")</f>
+        <f>IFERROR(IF((B3)&gt;0,(B5)/(B3),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="C6">
-        <f>IFERROR(C5/C3,"N/A")</f>
+        <f>IFERROR(IF((C3)&gt;0,(C5)/(C3),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="D6">
-        <f>IFERROR(D5/D3,"N/A")</f>
+        <f>IFERROR(IF((D3)&gt;0,(D5)/(D3),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="E6">
-        <f>IFERROR(E5/E3,"N/A")</f>
+        <f>IFERROR(IF((E3)&gt;0,(E5)/(E3),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="F6">
-        <f>IFERROR(F5/F3,"N/A")</f>
+        <f>IFERROR(IF((F3)&gt;0,(F5)/(F3),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="G6">
-        <f>IFERROR(G5/G3,"N/A")</f>
+        <f>IFERROR(IF((G3)&gt;0,(G5)/(G3),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="H6">
-        <f>IFERROR(H5/H3,"N/A")</f>
+        <f>IFERROR(IF((H3)&gt;0,(H5)/(H3),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="I6">
-        <f>IFERROR(I5/I3,"N/A")</f>
+        <f>IFERROR(IF((I3)&gt;0,(I5)/(I3),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="J6">
-        <f>IFERROR(J5/J3,"N/A")</f>
+        <f>IFERROR(IF((J3)&gt;0,(J5)/(J3),"N/A"),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -675,39 +926,39 @@
         </is>
       </c>
       <c r="B12">
-        <f>IFERROR(B11/B3,"N/A")</f>
+        <f>IFERROR(IF((B3)&gt;0,(B11)/(B3),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="C12">
-        <f>IFERROR(C11/C3,"N/A")</f>
+        <f>IFERROR(IF((C3)&gt;0,(C11)/(C3),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="D12">
-        <f>IFERROR(D11/D3,"N/A")</f>
+        <f>IFERROR(IF((D3)&gt;0,(D11)/(D3),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="E12">
-        <f>IFERROR(E11/E3,"N/A")</f>
+        <f>IFERROR(IF((E3)&gt;0,(E11)/(E3),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="F12">
-        <f>IFERROR(F11/F3,"N/A")</f>
+        <f>IFERROR(IF((F3)&gt;0,(F11)/(F3),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="G12">
-        <f>IFERROR(G11/G3,"N/A")</f>
+        <f>IFERROR(IF((G3)&gt;0,(G11)/(G3),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="H12">
-        <f>IFERROR(H11/H3,"N/A")</f>
+        <f>IFERROR(IF((H3)&gt;0,(H11)/(H3),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="I12">
-        <f>IFERROR(I11/I3,"N/A")</f>
+        <f>IFERROR(IF((I3)&gt;0,(I11)/(I3),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="J12">
-        <f>IFERROR(J11/J3,"N/A")</f>
+        <f>IFERROR(IF((J3)&gt;0,(J11)/(J3),"N/A"),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -896,39 +1147,39 @@
         </is>
       </c>
       <c r="B23">
-        <f>IFERROR(B13/(B14+B16),"N/A")</f>
+        <f>IFERROR(IF((B14+B16)&gt;0,(B13)/(B14+B16),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="C23">
-        <f>IFERROR(C13/(C14+C16),"N/A")</f>
+        <f>IFERROR(IF((C14+C16)&gt;0,(C13)/(C14+C16),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="D23">
-        <f>IFERROR(D13/(D14+D16),"N/A")</f>
+        <f>IFERROR(IF((D14+D16)&gt;0,(D13)/(D14+D16),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="E23">
-        <f>IFERROR(E13/(E14+E16),"N/A")</f>
+        <f>IFERROR(IF((E14+E16)&gt;0,(E13)/(E14+E16),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="F23">
-        <f>IFERROR(F13/(F14+F16),"N/A")</f>
+        <f>IFERROR(IF((F14+F16)&gt;0,(F13)/(F14+F16),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="G23">
-        <f>IFERROR(G13/(G14+G16),"N/A")</f>
+        <f>IFERROR(IF((G14+G16)&gt;0,(G13)/(G14+G16),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="H23">
-        <f>IFERROR(H13/(H14+H16),"N/A")</f>
+        <f>IFERROR(IF((H14+H16)&gt;0,(H13)/(H14+H16),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="I23">
-        <f>IFERROR(I13/(I14+I16),"N/A")</f>
+        <f>IFERROR(IF((I14+I16)&gt;0,(I13)/(I14+I16),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="J23">
-        <f>IFERROR(J13/(J14+J16),"N/A")</f>
+        <f>IFERROR(IF((J14+J16)&gt;0,(J13)/(J14+J16),"N/A"),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -939,39 +1190,39 @@
         </is>
       </c>
       <c r="B24">
-        <f>IFERROR(B11/B14,"N/A")</f>
+        <f>IFERROR(IF((B14)&gt;0,(B11)/(B14),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="C24">
-        <f>IFERROR(C11/C14,"N/A")</f>
+        <f>IFERROR(IF((C14)&gt;0,(C11)/(C14),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="D24">
-        <f>IFERROR(D11/D14,"N/A")</f>
+        <f>IFERROR(IF((D14)&gt;0,(D11)/(D14),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="E24">
-        <f>IFERROR(E11/E14,"N/A")</f>
+        <f>IFERROR(IF((E14)&gt;0,(E11)/(E14),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="F24">
-        <f>IFERROR(F11/F14,"N/A")</f>
+        <f>IFERROR(IF((F14)&gt;0,(F11)/(F14),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="G24">
-        <f>IFERROR(G11/G14,"N/A")</f>
+        <f>IFERROR(IF((G14)&gt;0,(G11)/(G14),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="H24">
-        <f>IFERROR(H11/H14,"N/A")</f>
+        <f>IFERROR(IF((H14)&gt;0,(H11)/(H14),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="I24">
-        <f>IFERROR(I11/I14,"N/A")</f>
+        <f>IFERROR(IF((I14)&gt;0,(I11)/(I14),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="J24">
-        <f>IFERROR(J11/J14,"N/A")</f>
+        <f>IFERROR(IF((J14)&gt;0,(J11)/(J14),"N/A"),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -982,39 +1233,39 @@
         </is>
       </c>
       <c r="B25">
-        <f>IFERROR(B13/B14,"N/A")</f>
+        <f>IFERROR(IF((B14)&gt;0,(B13)/(B14),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="C25">
-        <f>IFERROR(C13/C14,"N/A")</f>
+        <f>IFERROR(IF((C14)&gt;0,(C13)/(C14),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="D25">
-        <f>IFERROR(D13/D14,"N/A")</f>
+        <f>IFERROR(IF((D14)&gt;0,(D13)/(D14),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="E25">
-        <f>IFERROR(E13/E14,"N/A")</f>
+        <f>IFERROR(IF((E14)&gt;0,(E13)/(E14),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="F25">
-        <f>IFERROR(F13/F14,"N/A")</f>
+        <f>IFERROR(IF((F14)&gt;0,(F13)/(F14),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="G25">
-        <f>IFERROR(G13/G14,"N/A")</f>
+        <f>IFERROR(IF((G14)&gt;0,(G13)/(G14),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="H25">
-        <f>IFERROR(H13/H14,"N/A")</f>
+        <f>IFERROR(IF((H14)&gt;0,(H13)/(H14),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="I25">
-        <f>IFERROR(I13/I14,"N/A")</f>
+        <f>IFERROR(IF((I14)&gt;0,(I13)/(I14),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="J25">
-        <f>IFERROR(J13/J14,"N/A")</f>
+        <f>IFERROR(IF((J14)&gt;0,(J13)/(J14),"N/A"),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1068,39 +1319,39 @@
         </is>
       </c>
       <c r="B27">
-        <f>IFERROR(B26/B13,"N/A")</f>
+        <f>IFERROR(IF((B13)&gt;0,(B26)/(B13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="C27">
-        <f>IFERROR(C26/C13,"N/A")</f>
+        <f>IFERROR(IF((C13)&gt;0,(C26)/(C13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="D27">
-        <f>IFERROR(D26/D13,"N/A")</f>
+        <f>IFERROR(IF((D13)&gt;0,(D26)/(D13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="E27">
-        <f>IFERROR(E26/E13,"N/A")</f>
+        <f>IFERROR(IF((E13)&gt;0,(E26)/(E13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="F27">
-        <f>IFERROR(F26/F13,"N/A")</f>
+        <f>IFERROR(IF((F13)&gt;0,(F26)/(F13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="G27">
-        <f>IFERROR(G26/G13,"N/A")</f>
+        <f>IFERROR(IF((G13)&gt;0,(G26)/(G13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="H27">
-        <f>IFERROR(H26/H13,"N/A")</f>
+        <f>IFERROR(IF((H13)&gt;0,(H26)/(H13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="I27">
-        <f>IFERROR(I26/I13,"N/A")</f>
+        <f>IFERROR(IF((I13)&gt;0,(I26)/(I13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="J27">
-        <f>IFERROR(J26/J13,"N/A")</f>
+        <f>IFERROR(IF((J13)&gt;0,(J26)/(J13),"N/A"),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1631,39 +1882,39 @@
         </is>
       </c>
       <c r="B56">
-        <f>IFERROR((B40+B41+B44+B45)/B52,"N/A")</f>
+        <f>IFERROR(IF((B52)&gt;0,(B40+B41+B44+B45)/(B52),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="C56">
-        <f>IFERROR((C40+C41+C44+C45)/C52,"N/A")</f>
+        <f>IFERROR(IF((C52)&gt;0,(C40+C41+C44+C45)/(C52),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="D56">
-        <f>IFERROR((D40+D41+D44+D45)/D52,"N/A")</f>
+        <f>IFERROR(IF((D52)&gt;0,(D40+D41+D44+D45)/(D52),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="E56">
-        <f>IFERROR((E40+E41+E44+E45)/E52,"N/A")</f>
+        <f>IFERROR(IF((E52)&gt;0,(E40+E41+E44+E45)/(E52),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="F56">
-        <f>IFERROR((F40+F41+F44+F45)/F52,"N/A")</f>
+        <f>IFERROR(IF((F52)&gt;0,(F40+F41+F44+F45)/(F52),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="G56">
-        <f>IFERROR((G40+G41+G44+G45)/G52,"N/A")</f>
+        <f>IFERROR(IF((G52)&gt;0,(G40+G41+G44+G45)/(G52),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="H56">
-        <f>IFERROR((H40+H41+H44+H45)/H52,"N/A")</f>
+        <f>IFERROR(IF((H52)&gt;0,(H40+H41+H44+H45)/(H52),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="I56">
-        <f>IFERROR((I40+I41+I44+I45)/I52,"N/A")</f>
+        <f>IFERROR(IF((I52)&gt;0,(I40+I41+I44+I45)/(I52),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="J56">
-        <f>IFERROR((J40+J41+J44+J45)/J52,"N/A")</f>
+        <f>IFERROR(IF((J52)&gt;0,(J40+J41+J44+J45)/(J52),"N/A"),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1674,39 +1925,39 @@
         </is>
       </c>
       <c r="B57">
-        <f>IFERROR(B37/B43,"N/A")</f>
+        <f>IFERROR(IF((B43)&gt;0,(B37)/(B43),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="C57">
-        <f>IFERROR(C37/C43,"N/A")</f>
+        <f>IFERROR(IF((C43)&gt;0,(C37)/(C43),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="D57">
-        <f>IFERROR(D37/D43,"N/A")</f>
+        <f>IFERROR(IF((D43)&gt;0,(D37)/(D43),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="E57">
-        <f>IFERROR(E37/E43,"N/A")</f>
+        <f>IFERROR(IF((E43)&gt;0,(E37)/(E43),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="F57">
-        <f>IFERROR(F37/F43,"N/A")</f>
+        <f>IFERROR(IF((F43)&gt;0,(F37)/(F43),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="G57">
-        <f>IFERROR(G37/G43,"N/A")</f>
+        <f>IFERROR(IF((G43)&gt;0,(G37)/(G43),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="H57">
-        <f>IFERROR(H37/H43,"N/A")</f>
+        <f>IFERROR(IF((H43)&gt;0,(H37)/(H43),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="I57">
-        <f>IFERROR(I37/I43,"N/A")</f>
+        <f>IFERROR(IF((I43)&gt;0,(I37)/(I43),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="J57">
-        <f>IFERROR(J37/J43,"N/A")</f>
+        <f>IFERROR(IF((J43)&gt;0,(J37)/(J43),"N/A"),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1717,39 +1968,39 @@
         </is>
       </c>
       <c r="B58">
-        <f>IFERROR((B40+B41+B44+B45)/B13,"N/A")</f>
+        <f>IFERROR(IF((B13)&gt;0,(B40+B41+B44+B45)/(B13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="C58">
-        <f>IFERROR((C40+C41+C44+C45)/C13,"N/A")</f>
+        <f>IFERROR(IF((C13)&gt;0,(C40+C41+C44+C45)/(C13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="D58">
-        <f>IFERROR((D40+D41+D44+D45)/D13,"N/A")</f>
+        <f>IFERROR(IF((D13)&gt;0,(D40+D41+D44+D45)/(D13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="E58">
-        <f>IFERROR((E40+E41+E44+E45)/E13,"N/A")</f>
+        <f>IFERROR(IF((E13)&gt;0,(E40+E41+E44+E45)/(E13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="F58">
-        <f>IFERROR((F40+F41+F44+F45)/F13,"N/A")</f>
+        <f>IFERROR(IF((F13)&gt;0,(F40+F41+F44+F45)/(F13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="G58">
-        <f>IFERROR((G40+G41+G44+G45)/G13,"N/A")</f>
+        <f>IFERROR(IF((G13)&gt;0,(G40+G41+G44+G45)/(G13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="H58">
-        <f>IFERROR((H40+H41+H44+H45)/H13,"N/A")</f>
+        <f>IFERROR(IF((H13)&gt;0,(H40+H41+H44+H45)/(H13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="I58">
-        <f>IFERROR((I40+I41+I44+I45)/I13,"N/A")</f>
+        <f>IFERROR(IF((I13)&gt;0,(I40+I41+I44+I45)/(I13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="J58">
-        <f>IFERROR((J40+J41+J44+J45)/J13,"N/A")</f>
+        <f>IFERROR(IF((J13)&gt;0,(J40+J41+J44+J45)/(J13),"N/A"),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1760,39 +2011,39 @@
         </is>
       </c>
       <c r="B59">
-        <f>IFERROR((B40+B41+B44+B45-B33)/B13,"N/A")</f>
+        <f>IFERROR(IF((B13)&gt;0,(B40+B41+B44+B45-B33)/(B13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="C59">
-        <f>IFERROR((C40+C41+C44+C45-C33)/C13,"N/A")</f>
+        <f>IFERROR(IF((C13)&gt;0,(C40+C41+C44+C45-C33)/(C13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="D59">
-        <f>IFERROR((D40+D41+D44+D45-D33)/D13,"N/A")</f>
+        <f>IFERROR(IF((D13)&gt;0,(D40+D41+D44+D45-D33)/(D13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="E59">
-        <f>IFERROR((E40+E41+E44+E45-E33)/E13,"N/A")</f>
+        <f>IFERROR(IF((E13)&gt;0,(E40+E41+E44+E45-E33)/(E13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="F59">
-        <f>IFERROR((F40+F41+F44+F45-F33)/F13,"N/A")</f>
+        <f>IFERROR(IF((F13)&gt;0,(F40+F41+F44+F45-F33)/(F13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="G59">
-        <f>IFERROR((G40+G41+G44+G45-G33)/G13,"N/A")</f>
+        <f>IFERROR(IF((G13)&gt;0,(G40+G41+G44+G45-G33)/(G13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="H59">
-        <f>IFERROR((H40+H41+H44+H45-H33)/H13,"N/A")</f>
+        <f>IFERROR(IF((H13)&gt;0,(H40+H41+H44+H45-H33)/(H13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="I59">
-        <f>IFERROR((I40+I41+I44+I45-I33)/I13,"N/A")</f>
+        <f>IFERROR(IF((I13)&gt;0,(I40+I41+I44+I45-I33)/(I13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="J59">
-        <f>IFERROR((J40+J41+J44+J45-J33)/J13,"N/A")</f>
+        <f>IFERROR(IF((J13)&gt;0,(J40+J41+J44+J45-J33)/(J13),"N/A"),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1809,6 +2060,42 @@
           <t>Trade Debtor Days</t>
         </is>
       </c>
+      <c r="B61">
+        <f>IFERROR(IF((B3)&gt;0,(B34)/(B3)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="C61">
+        <f>IFERROR(IF((C3)&gt;0,(C34)/(C3)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="D61">
+        <f>IFERROR(IF((D3)&gt;0,(D34)/(D3)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="E61">
+        <f>IFERROR(IF((E3)&gt;0,(E34)/(E3)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="F61">
+        <f>IFERROR(IF((F3)&gt;0,(F34)/(F3)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="G61">
+        <f>IFERROR(IF((G3)&gt;0,(G34)/(G3)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="H61">
+        <f>IFERROR(IF((H3)&gt;0,(H34)/(H3)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="I61">
+        <f>IFERROR(IF((I3)&gt;0,(I34)/(I3)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="J61">
+        <f>IFERROR(IF((J3)&gt;0,(J34)/(J3)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1816,6 +2103,42 @@
           <t>Trade Creditor Days</t>
         </is>
       </c>
+      <c r="B62">
+        <f>IFERROR(IF((B4)&gt;0,(B39)/(B4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="C62">
+        <f>IFERROR(IF((C4)&gt;0,(C39)/(C4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="D62">
+        <f>IFERROR(IF((D4)&gt;0,(D39)/(D4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="E62">
+        <f>IFERROR(IF((E4)&gt;0,(E39)/(E4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="F62">
+        <f>IFERROR(IF((F4)&gt;0,(F39)/(F4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="G62">
+        <f>IFERROR(IF((G4)&gt;0,(G39)/(G4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="H62">
+        <f>IFERROR(IF((H4)&gt;0,(H39)/(H4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="I62">
+        <f>IFERROR(IF((I4)&gt;0,(I39)/(I4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="J62">
+        <f>IFERROR(IF((J4)&gt;0,(J39)/(J4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1823,6 +2146,42 @@
           <t>Stock Days</t>
         </is>
       </c>
+      <c r="B63">
+        <f>IFERROR(IF((B4)&gt;0,(B35)/(B4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="C63">
+        <f>IFERROR(IF((C4)&gt;0,(C35)/(C4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="D63">
+        <f>IFERROR(IF((D4)&gt;0,(D35)/(D4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="E63">
+        <f>IFERROR(IF((E4)&gt;0,(E35)/(E4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="F63">
+        <f>IFERROR(IF((F4)&gt;0,(F35)/(F4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="G63">
+        <f>IFERROR(IF((G4)&gt;0,(G35)/(G4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="H63">
+        <f>IFERROR(IF((H4)&gt;0,(H35)/(H4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="I63">
+        <f>IFERROR(IF((I4)&gt;0,(I35)/(I4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="J63">
+        <f>IFERROR(IF((J4)&gt;0,(J35)/(J4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1831,44 +2190,45 @@
         </is>
       </c>
       <c r="B64">
-        <f>B61+B63-B62</f>
+        <f>IFERROR(B61+B63-B62,"N/A")</f>
         <v/>
       </c>
       <c r="C64">
-        <f>C61+C63-C62</f>
+        <f>IFERROR(C61+C63-C62,"N/A")</f>
         <v/>
       </c>
       <c r="D64">
-        <f>D61+D63-D62</f>
+        <f>IFERROR(D61+D63-D62,"N/A")</f>
         <v/>
       </c>
       <c r="E64">
-        <f>E61+E63-E62</f>
+        <f>IFERROR(E61+E63-E62,"N/A")</f>
         <v/>
       </c>
       <c r="F64">
-        <f>F61+F63-F62</f>
+        <f>IFERROR(F61+F63-F62,"N/A")</f>
         <v/>
       </c>
       <c r="G64">
-        <f>G61+G63-G62</f>
+        <f>IFERROR(G61+G63-G62,"N/A")</f>
         <v/>
       </c>
       <c r="H64">
-        <f>H61+H63-H62</f>
+        <f>IFERROR(H61+H63-H62,"N/A")</f>
         <v/>
       </c>
       <c r="I64">
-        <f>I61+I63-I62</f>
+        <f>IFERROR(I61+I63-I62,"N/A")</f>
         <v/>
       </c>
       <c r="J64">
-        <f>J61+J63-J62</f>
+        <f>IFERROR(J61+J63-J62,"N/A")</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/templates/spreading/default_spreading_template.xlsx
+++ b/templates/spreading/default_spreading_template.xlsx
@@ -2301,7 +2301,7 @@
     </row>
     <row r="2">
       <c r="H2">
-        <f>IFERROR(G2/B2,"N/A")</f>
+        <f>IFERROR(IF(B2&gt;0,G2/B2,"N/A"),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
         <v/>
       </c>
       <c r="H3">
-        <f>IFERROR(G3/B3,"N/A")</f>
+        <f>IFERROR(IF(B3&gt;0,G3/B3,"N/A"),"N/A")</f>
         <v/>
       </c>
     </row>

--- a/templates/spreading/default_spreading_template.xlsx
+++ b/templates/spreading/default_spreading_template.xlsx
@@ -132,6 +132,257 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Leverage Trend</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Financial Spreading'!$A$58</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Financial Spreading'!$B$1:$G$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Financial Spreading'!$B$58:$G$58</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Financial Spreading'!$A$59</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Financial Spreading'!$B$1:$G$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Financial Spreading'!$B$59:$G$59</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Revenue Trend</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Financial Spreading'!$A$3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Financial Spreading'!$B$1:$G$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Financial Spreading'!$B$3:$G$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>65</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>83</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -561,39 +812,39 @@
         </is>
       </c>
       <c r="B6">
-        <f>IFERROR(B5/B3,"N/A")</f>
+        <f>IFERROR(IF((B3)&gt;0,(B5)/(B3),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="C6">
-        <f>IFERROR(C5/C3,"N/A")</f>
+        <f>IFERROR(IF((C3)&gt;0,(C5)/(C3),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="D6">
-        <f>IFERROR(D5/D3,"N/A")</f>
+        <f>IFERROR(IF((D3)&gt;0,(D5)/(D3),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="E6">
-        <f>IFERROR(E5/E3,"N/A")</f>
+        <f>IFERROR(IF((E3)&gt;0,(E5)/(E3),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="F6">
-        <f>IFERROR(F5/F3,"N/A")</f>
+        <f>IFERROR(IF((F3)&gt;0,(F5)/(F3),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="G6">
-        <f>IFERROR(G5/G3,"N/A")</f>
+        <f>IFERROR(IF((G3)&gt;0,(G5)/(G3),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="H6">
-        <f>IFERROR(H5/H3,"N/A")</f>
+        <f>IFERROR(IF((H3)&gt;0,(H5)/(H3),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="I6">
-        <f>IFERROR(I5/I3,"N/A")</f>
+        <f>IFERROR(IF((I3)&gt;0,(I5)/(I3),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="J6">
-        <f>IFERROR(J5/J3,"N/A")</f>
+        <f>IFERROR(IF((J3)&gt;0,(J5)/(J3),"N/A"),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -675,39 +926,39 @@
         </is>
       </c>
       <c r="B12">
-        <f>IFERROR(B11/B3,"N/A")</f>
+        <f>IFERROR(IF((B3)&gt;0,(B11)/(B3),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="C12">
-        <f>IFERROR(C11/C3,"N/A")</f>
+        <f>IFERROR(IF((C3)&gt;0,(C11)/(C3),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="D12">
-        <f>IFERROR(D11/D3,"N/A")</f>
+        <f>IFERROR(IF((D3)&gt;0,(D11)/(D3),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="E12">
-        <f>IFERROR(E11/E3,"N/A")</f>
+        <f>IFERROR(IF((E3)&gt;0,(E11)/(E3),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="F12">
-        <f>IFERROR(F11/F3,"N/A")</f>
+        <f>IFERROR(IF((F3)&gt;0,(F11)/(F3),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="G12">
-        <f>IFERROR(G11/G3,"N/A")</f>
+        <f>IFERROR(IF((G3)&gt;0,(G11)/(G3),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="H12">
-        <f>IFERROR(H11/H3,"N/A")</f>
+        <f>IFERROR(IF((H3)&gt;0,(H11)/(H3),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="I12">
-        <f>IFERROR(I11/I3,"N/A")</f>
+        <f>IFERROR(IF((I3)&gt;0,(I11)/(I3),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="J12">
-        <f>IFERROR(J11/J3,"N/A")</f>
+        <f>IFERROR(IF((J3)&gt;0,(J11)/(J3),"N/A"),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -896,39 +1147,39 @@
         </is>
       </c>
       <c r="B23">
-        <f>IFERROR(B13/(B14+B16),"N/A")</f>
+        <f>IFERROR(IF((B14+B16)&gt;0,(B13)/(B14+B16),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="C23">
-        <f>IFERROR(C13/(C14+C16),"N/A")</f>
+        <f>IFERROR(IF((C14+C16)&gt;0,(C13)/(C14+C16),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="D23">
-        <f>IFERROR(D13/(D14+D16),"N/A")</f>
+        <f>IFERROR(IF((D14+D16)&gt;0,(D13)/(D14+D16),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="E23">
-        <f>IFERROR(E13/(E14+E16),"N/A")</f>
+        <f>IFERROR(IF((E14+E16)&gt;0,(E13)/(E14+E16),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="F23">
-        <f>IFERROR(F13/(F14+F16),"N/A")</f>
+        <f>IFERROR(IF((F14+F16)&gt;0,(F13)/(F14+F16),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="G23">
-        <f>IFERROR(G13/(G14+G16),"N/A")</f>
+        <f>IFERROR(IF((G14+G16)&gt;0,(G13)/(G14+G16),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="H23">
-        <f>IFERROR(H13/(H14+H16),"N/A")</f>
+        <f>IFERROR(IF((H14+H16)&gt;0,(H13)/(H14+H16),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="I23">
-        <f>IFERROR(I13/(I14+I16),"N/A")</f>
+        <f>IFERROR(IF((I14+I16)&gt;0,(I13)/(I14+I16),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="J23">
-        <f>IFERROR(J13/(J14+J16),"N/A")</f>
+        <f>IFERROR(IF((J14+J16)&gt;0,(J13)/(J14+J16),"N/A"),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -939,39 +1190,39 @@
         </is>
       </c>
       <c r="B24">
-        <f>IFERROR(B11/B14,"N/A")</f>
+        <f>IFERROR(IF((B14)&gt;0,(B11)/(B14),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="C24">
-        <f>IFERROR(C11/C14,"N/A")</f>
+        <f>IFERROR(IF((C14)&gt;0,(C11)/(C14),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="D24">
-        <f>IFERROR(D11/D14,"N/A")</f>
+        <f>IFERROR(IF((D14)&gt;0,(D11)/(D14),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="E24">
-        <f>IFERROR(E11/E14,"N/A")</f>
+        <f>IFERROR(IF((E14)&gt;0,(E11)/(E14),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="F24">
-        <f>IFERROR(F11/F14,"N/A")</f>
+        <f>IFERROR(IF((F14)&gt;0,(F11)/(F14),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="G24">
-        <f>IFERROR(G11/G14,"N/A")</f>
+        <f>IFERROR(IF((G14)&gt;0,(G11)/(G14),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="H24">
-        <f>IFERROR(H11/H14,"N/A")</f>
+        <f>IFERROR(IF((H14)&gt;0,(H11)/(H14),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="I24">
-        <f>IFERROR(I11/I14,"N/A")</f>
+        <f>IFERROR(IF((I14)&gt;0,(I11)/(I14),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="J24">
-        <f>IFERROR(J11/J14,"N/A")</f>
+        <f>IFERROR(IF((J14)&gt;0,(J11)/(J14),"N/A"),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -982,39 +1233,39 @@
         </is>
       </c>
       <c r="B25">
-        <f>IFERROR(B13/B14,"N/A")</f>
+        <f>IFERROR(IF((B14)&gt;0,(B13)/(B14),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="C25">
-        <f>IFERROR(C13/C14,"N/A")</f>
+        <f>IFERROR(IF((C14)&gt;0,(C13)/(C14),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="D25">
-        <f>IFERROR(D13/D14,"N/A")</f>
+        <f>IFERROR(IF((D14)&gt;0,(D13)/(D14),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="E25">
-        <f>IFERROR(E13/E14,"N/A")</f>
+        <f>IFERROR(IF((E14)&gt;0,(E13)/(E14),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="F25">
-        <f>IFERROR(F13/F14,"N/A")</f>
+        <f>IFERROR(IF((F14)&gt;0,(F13)/(F14),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="G25">
-        <f>IFERROR(G13/G14,"N/A")</f>
+        <f>IFERROR(IF((G14)&gt;0,(G13)/(G14),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="H25">
-        <f>IFERROR(H13/H14,"N/A")</f>
+        <f>IFERROR(IF((H14)&gt;0,(H13)/(H14),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="I25">
-        <f>IFERROR(I13/I14,"N/A")</f>
+        <f>IFERROR(IF((I14)&gt;0,(I13)/(I14),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="J25">
-        <f>IFERROR(J13/J14,"N/A")</f>
+        <f>IFERROR(IF((J14)&gt;0,(J13)/(J14),"N/A"),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1068,39 +1319,39 @@
         </is>
       </c>
       <c r="B27">
-        <f>IFERROR(B26/B13,"N/A")</f>
+        <f>IFERROR(IF((B13)&gt;0,(B26)/(B13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="C27">
-        <f>IFERROR(C26/C13,"N/A")</f>
+        <f>IFERROR(IF((C13)&gt;0,(C26)/(C13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="D27">
-        <f>IFERROR(D26/D13,"N/A")</f>
+        <f>IFERROR(IF((D13)&gt;0,(D26)/(D13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="E27">
-        <f>IFERROR(E26/E13,"N/A")</f>
+        <f>IFERROR(IF((E13)&gt;0,(E26)/(E13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="F27">
-        <f>IFERROR(F26/F13,"N/A")</f>
+        <f>IFERROR(IF((F13)&gt;0,(F26)/(F13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="G27">
-        <f>IFERROR(G26/G13,"N/A")</f>
+        <f>IFERROR(IF((G13)&gt;0,(G26)/(G13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="H27">
-        <f>IFERROR(H26/H13,"N/A")</f>
+        <f>IFERROR(IF((H13)&gt;0,(H26)/(H13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="I27">
-        <f>IFERROR(I26/I13,"N/A")</f>
+        <f>IFERROR(IF((I13)&gt;0,(I26)/(I13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="J27">
-        <f>IFERROR(J26/J13,"N/A")</f>
+        <f>IFERROR(IF((J13)&gt;0,(J26)/(J13),"N/A"),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1631,39 +1882,39 @@
         </is>
       </c>
       <c r="B56">
-        <f>IFERROR((B40+B41+B44+B45)/B52,"N/A")</f>
+        <f>IFERROR(IF((B52)&gt;0,(B40+B41+B44+B45)/(B52),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="C56">
-        <f>IFERROR((C40+C41+C44+C45)/C52,"N/A")</f>
+        <f>IFERROR(IF((C52)&gt;0,(C40+C41+C44+C45)/(C52),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="D56">
-        <f>IFERROR((D40+D41+D44+D45)/D52,"N/A")</f>
+        <f>IFERROR(IF((D52)&gt;0,(D40+D41+D44+D45)/(D52),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="E56">
-        <f>IFERROR((E40+E41+E44+E45)/E52,"N/A")</f>
+        <f>IFERROR(IF((E52)&gt;0,(E40+E41+E44+E45)/(E52),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="F56">
-        <f>IFERROR((F40+F41+F44+F45)/F52,"N/A")</f>
+        <f>IFERROR(IF((F52)&gt;0,(F40+F41+F44+F45)/(F52),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="G56">
-        <f>IFERROR((G40+G41+G44+G45)/G52,"N/A")</f>
+        <f>IFERROR(IF((G52)&gt;0,(G40+G41+G44+G45)/(G52),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="H56">
-        <f>IFERROR((H40+H41+H44+H45)/H52,"N/A")</f>
+        <f>IFERROR(IF((H52)&gt;0,(H40+H41+H44+H45)/(H52),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="I56">
-        <f>IFERROR((I40+I41+I44+I45)/I52,"N/A")</f>
+        <f>IFERROR(IF((I52)&gt;0,(I40+I41+I44+I45)/(I52),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="J56">
-        <f>IFERROR((J40+J41+J44+J45)/J52,"N/A")</f>
+        <f>IFERROR(IF((J52)&gt;0,(J40+J41+J44+J45)/(J52),"N/A"),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1674,39 +1925,39 @@
         </is>
       </c>
       <c r="B57">
-        <f>IFERROR(B37/B43,"N/A")</f>
+        <f>IFERROR(IF((B43)&gt;0,(B37)/(B43),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="C57">
-        <f>IFERROR(C37/C43,"N/A")</f>
+        <f>IFERROR(IF((C43)&gt;0,(C37)/(C43),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="D57">
-        <f>IFERROR(D37/D43,"N/A")</f>
+        <f>IFERROR(IF((D43)&gt;0,(D37)/(D43),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="E57">
-        <f>IFERROR(E37/E43,"N/A")</f>
+        <f>IFERROR(IF((E43)&gt;0,(E37)/(E43),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="F57">
-        <f>IFERROR(F37/F43,"N/A")</f>
+        <f>IFERROR(IF((F43)&gt;0,(F37)/(F43),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="G57">
-        <f>IFERROR(G37/G43,"N/A")</f>
+        <f>IFERROR(IF((G43)&gt;0,(G37)/(G43),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="H57">
-        <f>IFERROR(H37/H43,"N/A")</f>
+        <f>IFERROR(IF((H43)&gt;0,(H37)/(H43),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="I57">
-        <f>IFERROR(I37/I43,"N/A")</f>
+        <f>IFERROR(IF((I43)&gt;0,(I37)/(I43),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="J57">
-        <f>IFERROR(J37/J43,"N/A")</f>
+        <f>IFERROR(IF((J43)&gt;0,(J37)/(J43),"N/A"),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1717,39 +1968,39 @@
         </is>
       </c>
       <c r="B58">
-        <f>IFERROR((B40+B41+B44+B45)/B13,"N/A")</f>
+        <f>IFERROR(IF((B13)&gt;0,(B40+B41+B44+B45)/(B13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="C58">
-        <f>IFERROR((C40+C41+C44+C45)/C13,"N/A")</f>
+        <f>IFERROR(IF((C13)&gt;0,(C40+C41+C44+C45)/(C13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="D58">
-        <f>IFERROR((D40+D41+D44+D45)/D13,"N/A")</f>
+        <f>IFERROR(IF((D13)&gt;0,(D40+D41+D44+D45)/(D13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="E58">
-        <f>IFERROR((E40+E41+E44+E45)/E13,"N/A")</f>
+        <f>IFERROR(IF((E13)&gt;0,(E40+E41+E44+E45)/(E13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="F58">
-        <f>IFERROR((F40+F41+F44+F45)/F13,"N/A")</f>
+        <f>IFERROR(IF((F13)&gt;0,(F40+F41+F44+F45)/(F13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="G58">
-        <f>IFERROR((G40+G41+G44+G45)/G13,"N/A")</f>
+        <f>IFERROR(IF((G13)&gt;0,(G40+G41+G44+G45)/(G13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="H58">
-        <f>IFERROR((H40+H41+H44+H45)/H13,"N/A")</f>
+        <f>IFERROR(IF((H13)&gt;0,(H40+H41+H44+H45)/(H13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="I58">
-        <f>IFERROR((I40+I41+I44+I45)/I13,"N/A")</f>
+        <f>IFERROR(IF((I13)&gt;0,(I40+I41+I44+I45)/(I13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="J58">
-        <f>IFERROR((J40+J41+J44+J45)/J13,"N/A")</f>
+        <f>IFERROR(IF((J13)&gt;0,(J40+J41+J44+J45)/(J13),"N/A"),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1760,39 +2011,39 @@
         </is>
       </c>
       <c r="B59">
-        <f>IFERROR((B40+B41+B44+B45-B33)/B13,"N/A")</f>
+        <f>IFERROR(IF((B13)&gt;0,(B40+B41+B44+B45-B33)/(B13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="C59">
-        <f>IFERROR((C40+C41+C44+C45-C33)/C13,"N/A")</f>
+        <f>IFERROR(IF((C13)&gt;0,(C40+C41+C44+C45-C33)/(C13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="D59">
-        <f>IFERROR((D40+D41+D44+D45-D33)/D13,"N/A")</f>
+        <f>IFERROR(IF((D13)&gt;0,(D40+D41+D44+D45-D33)/(D13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="E59">
-        <f>IFERROR((E40+E41+E44+E45-E33)/E13,"N/A")</f>
+        <f>IFERROR(IF((E13)&gt;0,(E40+E41+E44+E45-E33)/(E13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="F59">
-        <f>IFERROR((F40+F41+F44+F45-F33)/F13,"N/A")</f>
+        <f>IFERROR(IF((F13)&gt;0,(F40+F41+F44+F45-F33)/(F13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="G59">
-        <f>IFERROR((G40+G41+G44+G45-G33)/G13,"N/A")</f>
+        <f>IFERROR(IF((G13)&gt;0,(G40+G41+G44+G45-G33)/(G13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="H59">
-        <f>IFERROR((H40+H41+H44+H45-H33)/H13,"N/A")</f>
+        <f>IFERROR(IF((H13)&gt;0,(H40+H41+H44+H45-H33)/(H13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="I59">
-        <f>IFERROR((I40+I41+I44+I45-I33)/I13,"N/A")</f>
+        <f>IFERROR(IF((I13)&gt;0,(I40+I41+I44+I45-I33)/(I13),"N/A"),"N/A")</f>
         <v/>
       </c>
       <c r="J59">
-        <f>IFERROR((J40+J41+J44+J45-J33)/J13,"N/A")</f>
+        <f>IFERROR(IF((J13)&gt;0,(J40+J41+J44+J45-J33)/(J13),"N/A"),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1809,6 +2060,42 @@
           <t>Trade Debtor Days</t>
         </is>
       </c>
+      <c r="B61">
+        <f>IFERROR(IF((B3)&gt;0,(B34)/(B3)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="C61">
+        <f>IFERROR(IF((C3)&gt;0,(C34)/(C3)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="D61">
+        <f>IFERROR(IF((D3)&gt;0,(D34)/(D3)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="E61">
+        <f>IFERROR(IF((E3)&gt;0,(E34)/(E3)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="F61">
+        <f>IFERROR(IF((F3)&gt;0,(F34)/(F3)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="G61">
+        <f>IFERROR(IF((G3)&gt;0,(G34)/(G3)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="H61">
+        <f>IFERROR(IF((H3)&gt;0,(H34)/(H3)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="I61">
+        <f>IFERROR(IF((I3)&gt;0,(I34)/(I3)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="J61">
+        <f>IFERROR(IF((J3)&gt;0,(J34)/(J3)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1816,6 +2103,42 @@
           <t>Trade Creditor Days</t>
         </is>
       </c>
+      <c r="B62">
+        <f>IFERROR(IF((B4)&gt;0,(B39)/(B4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="C62">
+        <f>IFERROR(IF((C4)&gt;0,(C39)/(C4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="D62">
+        <f>IFERROR(IF((D4)&gt;0,(D39)/(D4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="E62">
+        <f>IFERROR(IF((E4)&gt;0,(E39)/(E4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="F62">
+        <f>IFERROR(IF((F4)&gt;0,(F39)/(F4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="G62">
+        <f>IFERROR(IF((G4)&gt;0,(G39)/(G4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="H62">
+        <f>IFERROR(IF((H4)&gt;0,(H39)/(H4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="I62">
+        <f>IFERROR(IF((I4)&gt;0,(I39)/(I4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="J62">
+        <f>IFERROR(IF((J4)&gt;0,(J39)/(J4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1823,6 +2146,42 @@
           <t>Stock Days</t>
         </is>
       </c>
+      <c r="B63">
+        <f>IFERROR(IF((B4)&gt;0,(B35)/(B4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="C63">
+        <f>IFERROR(IF((C4)&gt;0,(C35)/(C4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="D63">
+        <f>IFERROR(IF((D4)&gt;0,(D35)/(D4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="E63">
+        <f>IFERROR(IF((E4)&gt;0,(E35)/(E4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="F63">
+        <f>IFERROR(IF((F4)&gt;0,(F35)/(F4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="G63">
+        <f>IFERROR(IF((G4)&gt;0,(G35)/(G4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="H63">
+        <f>IFERROR(IF((H4)&gt;0,(H35)/(H4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="I63">
+        <f>IFERROR(IF((I4)&gt;0,(I35)/(I4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
+      <c r="J63">
+        <f>IFERROR(IF((J4)&gt;0,(J35)/(J4)*365,"N/A"),"N/A")</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1831,44 +2190,45 @@
         </is>
       </c>
       <c r="B64">
-        <f>B61+B63-B62</f>
+        <f>IFERROR(B61+B63-B62,"N/A")</f>
         <v/>
       </c>
       <c r="C64">
-        <f>C61+C63-C62</f>
+        <f>IFERROR(C61+C63-C62,"N/A")</f>
         <v/>
       </c>
       <c r="D64">
-        <f>D61+D63-D62</f>
+        <f>IFERROR(D61+D63-D62,"N/A")</f>
         <v/>
       </c>
       <c r="E64">
-        <f>E61+E63-E62</f>
+        <f>IFERROR(E61+E63-E62,"N/A")</f>
         <v/>
       </c>
       <c r="F64">
-        <f>F61+F63-F62</f>
+        <f>IFERROR(F61+F63-F62,"N/A")</f>
         <v/>
       </c>
       <c r="G64">
-        <f>G61+G63-G62</f>
+        <f>IFERROR(G61+G63-G62,"N/A")</f>
         <v/>
       </c>
       <c r="H64">
-        <f>H61+H63-H62</f>
+        <f>IFERROR(H61+H63-H62,"N/A")</f>
         <v/>
       </c>
       <c r="I64">
-        <f>I61+I63-I62</f>
+        <f>IFERROR(I61+I63-I62,"N/A")</f>
         <v/>
       </c>
       <c r="J64">
-        <f>J61+J63-J62</f>
+        <f>IFERROR(J61+J63-J62,"N/A")</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1941,7 +2301,7 @@
     </row>
     <row r="2">
       <c r="H2">
-        <f>IFERROR(G2/B2,"N/A")</f>
+        <f>IFERROR(IF(B2&gt;0,G2/B2,"N/A"),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1976,7 +2336,7 @@
         <v/>
       </c>
       <c r="H3">
-        <f>IFERROR(G3/B3,"N/A")</f>
+        <f>IFERROR(IF(B3&gt;0,G3/B3,"N/A"),"N/A")</f>
         <v/>
       </c>
     </row>

--- a/templates/spreading/default_spreading_template.xlsx
+++ b/templates/spreading/default_spreading_template.xlsx
@@ -153,8 +153,10 @@
       </tx>
     </title>
     <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
@@ -168,14 +170,6 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
           <cat>
             <numRef>
               <f>'Financial Spreading'!$B$1:$G$1</f>
@@ -200,14 +194,6 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
           <cat>
             <numRef>
               <f>'Financial Spreading'!$B$1:$G$1</f>
@@ -219,14 +205,16 @@
             </numRef>
           </val>
         </ser>
+        <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
-      </lineChart>
+      </barChart>
       <catAx>
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -238,6 +226,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <majorTickMark val="none"/>
@@ -276,6 +265,7 @@
       <barChart>
         <barDir val="col"/>
         <grouping val="clustered"/>
+        <varyColors val="0"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
@@ -309,6 +299,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -320,6 +311,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <majorTickMark val="none"/>

--- a/templates/spreading/default_spreading_template.xlsx
+++ b/templates/spreading/default_spreading_template.xlsx
@@ -957,7 +957,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EBITDA</t>
+          <t>EBITDA (before exceptionals, incl. other income)</t>
         </is>
       </c>
       <c r="B13">
@@ -1135,7 +1135,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DSCR</t>
+          <t>DSCR (EBITDA-based)</t>
         </is>
       </c>
       <c r="B23">
@@ -1264,7 +1264,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FCF</t>
+          <t>FCF (before working capital)</t>
         </is>
       </c>
       <c r="B26">
@@ -1307,7 +1307,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FCF Conversion %</t>
+          <t>FCF Conversion % (before working capital)</t>
         </is>
       </c>
       <c r="B27">

--- a/templates/spreading/default_spreading_template.xlsx
+++ b/templates/spreading/default_spreading_template.xlsx
@@ -334,7 +334,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>65</row>
+      <row>66</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2700000"/>
@@ -356,7 +356,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>83</row>
+      <row>84</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2700000"/>
@@ -666,7 +666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2215,6 +2215,49 @@
       </c>
       <c r="J64">
         <f>IFERROR(J61+J63-J62,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>FCF after Working Capital</t>
+        </is>
+      </c>
+      <c r="B65">
+        <f>IF(COUNT(A34,A35,A36,A39,A42)=0,"N/A",B26-((B34+B35+B36-B39-B42)-(A34+A35+A36-A39-A42)))</f>
+        <v/>
+      </c>
+      <c r="C65">
+        <f>IF(COUNT(B34,B35,B36,B39,B42)=0,"N/A",C26-((C34+C35+C36-C39-C42)-(B34+B35+B36-B39-B42)))</f>
+        <v/>
+      </c>
+      <c r="D65">
+        <f>IF(COUNT(C34,C35,C36,C39,C42)=0,"N/A",D26-((D34+D35+D36-D39-D42)-(C34+C35+C36-C39-C42)))</f>
+        <v/>
+      </c>
+      <c r="E65">
+        <f>IF(COUNT(D34,D35,D36,D39,D42)=0,"N/A",E26-((E34+E35+E36-E39-E42)-(D34+D35+D36-D39-D42)))</f>
+        <v/>
+      </c>
+      <c r="F65">
+        <f>IF(COUNT(E34,E35,E36,E39,E42)=0,"N/A",F26-((F34+F35+F36-F39-F42)-(E34+E35+E36-E39-E42)))</f>
+        <v/>
+      </c>
+      <c r="G65">
+        <f>IF(COUNT(F34,F35,F36,F39,F42)=0,"N/A",G26-((G34+G35+G36-G39-G42)-(F34+F35+F36-F39-F42)))</f>
+        <v/>
+      </c>
+      <c r="H65">
+        <f>IF(COUNT(G34,G35,G36,G39,G42)=0,"N/A",H26-((H34+H35+H36-H39-H42)-(G34+G35+G36-G39-G42)))</f>
+        <v/>
+      </c>
+      <c r="I65">
+        <f>IF(COUNT(H34,H35,H36,H39,H42)=0,"N/A",I26-((I34+I35+I36-I39-I42)-(H34+H35+H36-H39-H42)))</f>
+        <v/>
+      </c>
+      <c r="J65">
+        <f>IF(COUNT(I34,I35,I36,I39,I42)=0,"N/A",J26-((J34+J35+J36-J39-J42)-(I34+I35+I36-I39-I42)))</f>
         <v/>
       </c>
     </row>
